--- a/游戏设计王/老虎机数学专题-免费游戏触发.xlsx
+++ b/游戏设计王/老虎机数学专题-免费游戏触发.xlsx
@@ -1177,7 +1177,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1266,6 +1266,12 @@
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4420,15 +4426,15 @@
       <c r="A5" s="3">
         <v>25</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="46">
         <f t="shared" ref="B5:B24" si="0">(1-1/A5)^A5</f>
         <v>0.360396716858018</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="46">
         <f t="shared" ref="C5:C24" si="1">(1-1/A5)^(2*A5)</f>
         <v>0.129885793522038</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="46">
         <f t="shared" ref="D5:D24" si="2">(1-1/A5)^(3*A5)</f>
         <v>0.0468104135518411</v>
       </c>
@@ -4446,15 +4452,15 @@
       <c r="A6" s="3">
         <v>50</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="46">
         <f t="shared" si="0"/>
         <v>0.364169680087117</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="46">
         <f t="shared" si="1"/>
         <v>0.132619555894753</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="46">
         <f t="shared" si="2"/>
         <v>0.0482960212434877</v>
       </c>
@@ -4472,15 +4478,15 @@
       <c r="A7" s="3">
         <v>75</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="46">
         <f t="shared" si="0"/>
         <v>0.365413194878888</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="46">
         <f t="shared" si="1"/>
         <v>0.133526802991596</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="46">
         <f t="shared" si="2"/>
         <v>0.0487924556831229</v>
       </c>
@@ -4498,15 +4504,15 @@
       <c r="A8" s="3">
         <v>100</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="46">
         <f t="shared" si="0"/>
         <v>0.366032341273229</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="46">
         <f t="shared" si="1"/>
         <v>0.133979674857962</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="46">
         <f t="shared" si="2"/>
         <v>0.0490408940712857</v>
       </c>
@@ -4524,15 +4530,15 @@
       <c r="A9" s="3">
         <v>125</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="46">
         <f t="shared" si="0"/>
         <v>0.366402998638711</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="46">
         <f t="shared" si="1"/>
         <v>0.134251157411439</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="46">
         <f t="shared" si="2"/>
         <v>0.049190026646269</v>
       </c>
@@ -4550,15 +4556,15 @@
       <c r="A10" s="3">
         <v>150</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="46">
         <f t="shared" si="0"/>
         <v>0.36664975867942</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="46">
         <f t="shared" si="1"/>
         <v>0.134432045539677</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="46">
         <f t="shared" si="2"/>
         <v>0.0492894770559035</v>
       </c>
@@ -4576,15 +4582,15 @@
       <c r="A11" s="3">
         <v>175</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="46">
         <f t="shared" si="0"/>
         <v>0.366825847299319</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="46">
         <f t="shared" si="1"/>
         <v>0.134561202246863</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="46">
         <f t="shared" si="2"/>
         <v>0.0493605270278205</v>
       </c>
@@ -4602,15 +4608,15 @@
       <c r="A12" s="3">
         <v>200</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="46">
         <f t="shared" si="0"/>
         <v>0.366957821726167</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="46">
         <f t="shared" si="1"/>
         <v>0.134658042926013</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="46">
         <f t="shared" si="2"/>
         <v>0.0494138221100386</v>
       </c>
@@ -4628,15 +4634,15 @@
       <c r="A13" s="3">
         <v>225</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="46">
         <f t="shared" si="0"/>
         <v>0.367060414022346</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="46">
         <f t="shared" si="1"/>
         <v>0.134733347542256</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="46">
         <f t="shared" si="2"/>
         <v>0.049455278331477</v>
       </c>
@@ -4654,15 +4660,15 @@
       <c r="A14" s="3">
         <v>250</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="46">
         <f t="shared" si="0"/>
         <v>0.367142453566242</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="46">
         <f t="shared" si="1"/>
         <v>0.13479358121064</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="46">
         <f t="shared" si="2"/>
         <v>0.049488446130655</v>
       </c>
@@ -4680,15 +4686,15 @@
       <c r="A15" s="3">
         <v>300</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="46">
         <f t="shared" si="0"/>
         <v>0.367265455774763</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="46">
         <f t="shared" si="1"/>
         <v>0.134883915005444</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="46">
         <f t="shared" si="2"/>
         <v>0.0495382025211588</v>
       </c>
@@ -4706,15 +4712,15 @@
       <c r="A16" s="3">
         <v>350</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="46">
         <f t="shared" si="0"/>
         <v>0.367353272572098</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="46">
         <f t="shared" si="1"/>
         <v>0.13494842686943</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="46">
         <f t="shared" si="2"/>
         <v>0.0495737462389414</v>
       </c>
@@ -4732,15 +4738,15 @@
       <c r="A17" s="3">
         <v>400</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="46">
         <f t="shared" si="0"/>
         <v>0.367419112260693</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="46">
         <f t="shared" si="1"/>
         <v>0.134996804054436</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="46">
         <f t="shared" si="2"/>
         <v>0.0496004059037114</v>
       </c>
@@ -4758,15 +4764,15 @@
       <c r="A18" s="3">
         <v>450</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="46">
         <f t="shared" si="0"/>
         <v>0.367470307338958</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="46">
         <f t="shared" si="1"/>
         <v>0.135034426775788</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="46">
         <f t="shared" si="2"/>
         <v>0.0496211423086391</v>
       </c>
@@ -4784,15 +4790,15 @@
       <c r="A19" s="3">
         <v>500</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="46">
         <f t="shared" si="0"/>
         <v>0.367511254857159</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="46">
         <f t="shared" si="1"/>
         <v>0.135064522446683</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="46">
         <f t="shared" si="2"/>
         <v>0.0496377321310635</v>
       </c>
@@ -4810,15 +4816,15 @@
       <c r="A20" s="3">
         <v>600</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="46">
         <f t="shared" si="0"/>
         <v>0.367572661899685</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="46">
         <f t="shared" si="1"/>
         <v>0.13510966177602</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="46">
         <f t="shared" si="2"/>
         <v>0.0496626180273779</v>
       </c>
@@ -4836,15 +4842,15 @@
       <c r="A21" s="3">
         <v>700</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="46">
         <f t="shared" si="0"/>
         <v>0.367616513618891</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="46">
         <f t="shared" si="1"/>
         <v>0.135141901085308</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="46">
         <f t="shared" si="2"/>
         <v>0.0496803945208099</v>
       </c>
@@ -4862,15 +4868,15 @@
       <c r="A22" s="3">
         <v>800</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="46">
         <f t="shared" si="0"/>
         <v>0.367649396693398</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="46">
         <f t="shared" si="1"/>
         <v>0.135166078889019</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="46">
         <f t="shared" si="2"/>
         <v>0.0496937273569602</v>
       </c>
@@ -4888,15 +4894,15 @@
       <c r="A23" s="3">
         <v>900</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="46">
         <f t="shared" si="0"/>
         <v>0.367674969032344</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="46">
         <f t="shared" si="1"/>
         <v>0.135184882852935</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="46">
         <f t="shared" si="2"/>
         <v>0.049704097616594</v>
       </c>
@@ -4914,15 +4920,15 @@
       <c r="A24" s="3">
         <v>1000</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="46">
         <f t="shared" si="0"/>
         <v>0.367695424770964</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="46">
         <f t="shared" si="1"/>
         <v>0.135199925397499</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="46">
         <f t="shared" si="2"/>
         <v>0.0497123939980362</v>
       </c>
@@ -5059,11 +5065,11 @@
         <f t="shared" ref="B30:B49" si="3">INT(LN(0.5)/LN(1-1/A30))</f>
         <v>16</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="46">
         <f t="shared" ref="C30:C49" si="4">1-(1-1/A30)^B30</f>
         <v>0.479597075333528</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="48">
         <f t="shared" ref="D30:D49" si="5">B30/A30</f>
         <v>0.64</v>
       </c>
@@ -5085,11 +5091,11 @@
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="46">
         <f t="shared" si="4"/>
         <v>0.496862632022369</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="48">
         <f t="shared" si="5"/>
         <v>0.68</v>
       </c>
@@ -5111,11 +5117,11 @@
         <f t="shared" si="3"/>
         <v>51</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="46">
         <f t="shared" si="4"/>
         <v>0.495695000869351</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="48">
         <f t="shared" si="5"/>
         <v>0.68</v>
       </c>
@@ -5137,11 +5143,11 @@
         <f t="shared" si="3"/>
         <v>68</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="46">
         <f t="shared" si="4"/>
         <v>0.49511411121293</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="48">
         <f t="shared" si="5"/>
         <v>0.68</v>
       </c>
@@ -5163,11 +5169,11 @@
         <f t="shared" si="3"/>
         <v>86</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="46">
         <f t="shared" si="4"/>
         <v>0.498808374984284</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="48">
         <f t="shared" si="5"/>
         <v>0.688</v>
       </c>
@@ -5189,11 +5195,11 @@
         <f t="shared" si="3"/>
         <v>103</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="46">
         <f t="shared" si="4"/>
         <v>0.497904922358701</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="48">
         <f t="shared" si="5"/>
         <v>0.686666666666667</v>
       </c>
@@ -5215,11 +5221,11 @@
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="46">
         <f t="shared" si="4"/>
         <v>0.497259408751929</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="48">
         <f t="shared" si="5"/>
         <v>0.685714285714286</v>
       </c>
@@ -5241,11 +5247,11 @@
         <f t="shared" si="3"/>
         <v>138</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="46">
         <f t="shared" si="4"/>
         <v>0.499291293754147</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="48">
         <f t="shared" si="5"/>
         <v>0.69</v>
       </c>
@@ -5267,11 +5273,11 @@
         <f t="shared" si="3"/>
         <v>155</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="46">
         <f t="shared" si="4"/>
         <v>0.498636706599578</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="48">
         <f t="shared" si="5"/>
         <v>0.688888888888889</v>
       </c>
@@ -5293,11 +5299,11 @@
         <f t="shared" si="3"/>
         <v>172</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="46">
         <f t="shared" si="4"/>
         <v>0.498112696933415</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="48">
         <f t="shared" si="5"/>
         <v>0.688</v>
       </c>
@@ -5319,11 +5325,11 @@
         <f t="shared" si="3"/>
         <v>207</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="46">
         <f t="shared" si="4"/>
         <v>0.49900169541332</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="48">
         <f t="shared" si="5"/>
         <v>0.69</v>
       </c>
@@ -5345,11 +5351,11 @@
         <f t="shared" si="3"/>
         <v>242</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="46">
         <f t="shared" si="4"/>
         <v>0.499635382843854</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="48">
         <f t="shared" si="5"/>
         <v>0.691428571428571</v>
       </c>
@@ -5371,11 +5377,11 @@
         <f t="shared" si="3"/>
         <v>276</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="46">
         <f t="shared" si="4"/>
         <v>0.498857075531263</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="48">
         <f t="shared" si="5"/>
         <v>0.69</v>
       </c>
@@ -5397,11 +5403,11 @@
         <f t="shared" si="3"/>
         <v>311</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="46">
         <f t="shared" si="4"/>
         <v>0.499366084148335</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="48">
         <f t="shared" si="5"/>
         <v>0.691111111111111</v>
       </c>
@@ -5423,11 +5429,11 @@
         <f t="shared" si="3"/>
         <v>346</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="46">
         <f t="shared" si="4"/>
         <v>0.499772820151414</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="48">
         <f t="shared" si="5"/>
         <v>0.692</v>
       </c>
@@ -5449,11 +5455,11 @@
         <f t="shared" si="3"/>
         <v>415</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="46">
         <f t="shared" si="4"/>
         <v>0.499548053982464</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="48">
         <f t="shared" si="5"/>
         <v>0.691666666666667</v>
       </c>
@@ -5475,11 +5481,11 @@
         <f t="shared" si="3"/>
         <v>484</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="46">
         <f t="shared" si="4"/>
         <v>0.499387494785346</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="48">
         <f t="shared" si="5"/>
         <v>0.691428571428571</v>
       </c>
@@ -5501,11 +5507,11 @@
         <f t="shared" si="3"/>
         <v>554</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="46">
         <f t="shared" si="4"/>
         <v>0.499892985027228</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="48">
         <f t="shared" si="5"/>
         <v>0.6925</v>
       </c>
@@ -5527,11 +5533,11 @@
         <f t="shared" si="3"/>
         <v>623</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="46">
         <f t="shared" si="4"/>
         <v>0.499729874391522</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="48">
         <f t="shared" si="5"/>
         <v>0.692222222222222</v>
       </c>
@@ -5553,11 +5559,11 @@
         <f t="shared" si="3"/>
         <v>692</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="46">
         <f t="shared" si="4"/>
         <v>0.499599364716989</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="48">
         <f t="shared" si="5"/>
         <v>0.692</v>
       </c>
@@ -5852,11 +5858,11 @@
       <c r="A62" s="3">
         <v>1</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="48">
         <f t="shared" ref="B62:B125" si="6">(1-1/$B$59)^($A62-1)*(1/$B$59)</f>
         <v>0.01</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="48">
         <f>SUM($B$62:$B62)</f>
         <v>0.01</v>
       </c>
@@ -5877,11 +5883,11 @@
       <c r="A63" s="3">
         <v>2</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="48">
         <f t="shared" si="6"/>
         <v>0.0099</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63" s="48">
         <f>SUM($B$62:$B63)</f>
         <v>0.0199</v>
       </c>
@@ -5902,11 +5908,11 @@
       <c r="A64" s="3">
         <v>3</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="48">
         <f t="shared" si="6"/>
         <v>0.009801</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="48">
         <f>SUM($B$62:$B64)</f>
         <v>0.029701</v>
       </c>
@@ -5927,11 +5933,11 @@
       <c r="A65" s="3">
         <v>4</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="48">
         <f t="shared" si="6"/>
         <v>0.00970299</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65" s="48">
         <f>SUM($B$62:$B65)</f>
         <v>0.03940399</v>
       </c>
@@ -5952,11 +5958,11 @@
       <c r="A66" s="3">
         <v>5</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="48">
         <f t="shared" si="6"/>
         <v>0.0096059601</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="48">
         <f>SUM($B$62:$B66)</f>
         <v>0.0490099501</v>
       </c>
@@ -5977,11 +5983,11 @@
       <c r="A67" s="3">
         <v>6</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="48">
         <f t="shared" si="6"/>
         <v>0.009509900499</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C67" s="48">
         <f>SUM($B$62:$B67)</f>
         <v>0.058519850599</v>
       </c>
@@ -6002,11 +6008,11 @@
       <c r="A68" s="3">
         <v>7</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="48">
         <f t="shared" si="6"/>
         <v>0.00941480149401</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="48">
         <f>SUM($B$62:$B68)</f>
         <v>0.06793465209301</v>
       </c>
@@ -6027,11 +6033,11 @@
       <c r="A69" s="3">
         <v>8</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="48">
         <f t="shared" si="6"/>
         <v>0.0093206534790699</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69" s="48">
         <f>SUM($B$62:$B69)</f>
         <v>0.0772553055720799</v>
       </c>
@@ -6052,11 +6058,11 @@
       <c r="A70" s="3">
         <v>9</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="48">
         <f t="shared" si="6"/>
         <v>0.0092274469442792</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="48">
         <f>SUM($B$62:$B70)</f>
         <v>0.0864827525163591</v>
       </c>
@@ -6077,11 +6083,11 @@
       <c r="A71" s="3">
         <v>10</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="48">
         <f t="shared" si="6"/>
         <v>0.00913517247483641</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C71" s="48">
         <f>SUM($B$62:$B71)</f>
         <v>0.0956179249911955</v>
       </c>
@@ -6102,11 +6108,11 @@
       <c r="A72" s="3">
         <v>11</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="48">
         <f t="shared" si="6"/>
         <v>0.00904382075008804</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C72" s="48">
         <f>SUM($B$62:$B72)</f>
         <v>0.104661745741284</v>
       </c>
@@ -6127,11 +6133,11 @@
       <c r="A73" s="3">
         <v>12</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="48">
         <f t="shared" si="6"/>
         <v>0.00895338254258716</v>
       </c>
-      <c r="C73" s="9">
+      <c r="C73" s="48">
         <f>SUM($B$62:$B73)</f>
         <v>0.113615128283871</v>
       </c>
@@ -6152,11 +6158,11 @@
       <c r="A74" s="3">
         <v>13</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="48">
         <f t="shared" si="6"/>
         <v>0.00886384871716129</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="48">
         <f>SUM($B$62:$B74)</f>
         <v>0.122478977001032</v>
       </c>
@@ -6177,11 +6183,11 @@
       <c r="A75" s="3">
         <v>14</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="48">
         <f t="shared" si="6"/>
         <v>0.00877521022998968</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C75" s="48">
         <f>SUM($B$62:$B75)</f>
         <v>0.131254187231022</v>
       </c>
@@ -6202,11 +6208,11 @@
       <c r="A76" s="3">
         <v>15</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="48">
         <f t="shared" si="6"/>
         <v>0.00868745812768978</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="48">
         <f>SUM($B$62:$B76)</f>
         <v>0.139941645358711</v>
       </c>
@@ -6227,11 +6233,11 @@
       <c r="A77" s="3">
         <v>16</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="48">
         <f t="shared" si="6"/>
         <v>0.00860058354641288</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C77" s="48">
         <f>SUM($B$62:$B77)</f>
         <v>0.148542228905124</v>
       </c>
@@ -6252,11 +6258,11 @@
       <c r="A78" s="3">
         <v>17</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="48">
         <f t="shared" si="6"/>
         <v>0.00851457771094876</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="48">
         <f>SUM($B$62:$B78)</f>
         <v>0.157056806616073</v>
       </c>
@@ -6277,11 +6283,11 @@
       <c r="A79" s="3">
         <v>18</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="48">
         <f t="shared" si="6"/>
         <v>0.00842943193383927</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79" s="48">
         <f>SUM($B$62:$B79)</f>
         <v>0.165486238549912</v>
       </c>
@@ -6302,11 +6308,11 @@
       <c r="A80" s="3">
         <v>19</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="48">
         <f t="shared" si="6"/>
         <v>0.00834513761450087</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="48">
         <f>SUM($B$62:$B80)</f>
         <v>0.173831376164413</v>
       </c>
@@ -6327,11 +6333,11 @@
       <c r="A81" s="3">
         <v>20</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="48">
         <f t="shared" si="6"/>
         <v>0.00826168623835587</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81" s="48">
         <f>SUM($B$62:$B81)</f>
         <v>0.182093062402769</v>
       </c>
@@ -6352,11 +6358,11 @@
       <c r="A82" s="3">
         <v>21</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="48">
         <f t="shared" si="6"/>
         <v>0.00817906937597231</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="48">
         <f>SUM($B$62:$B82)</f>
         <v>0.190272131778741</v>
       </c>
@@ -6377,11 +6383,11 @@
       <c r="A83" s="3">
         <v>22</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="48">
         <f t="shared" si="6"/>
         <v>0.00809727868221258</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83" s="48">
         <f>SUM($B$62:$B83)</f>
         <v>0.198369410460954</v>
       </c>
@@ -6402,11 +6408,11 @@
       <c r="A84" s="3">
         <v>23</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="48">
         <f t="shared" si="6"/>
         <v>0.00801630589539046</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="48">
         <f>SUM($B$62:$B84)</f>
         <v>0.206385716356344</v>
       </c>
@@ -6427,11 +6433,11 @@
       <c r="A85" s="3">
         <v>24</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="48">
         <f t="shared" si="6"/>
         <v>0.00793614283643655</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="48">
         <f>SUM($B$62:$B85)</f>
         <v>0.214321859192781</v>
       </c>
@@ -6452,11 +6458,11 @@
       <c r="A86" s="3">
         <v>25</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="48">
         <f t="shared" si="6"/>
         <v>0.00785678140807219</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="48">
         <f>SUM($B$62:$B86)</f>
         <v>0.222178640600853</v>
       </c>
@@ -6477,11 +6483,11 @@
       <c r="A87" s="3">
         <v>26</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="48">
         <f t="shared" si="6"/>
         <v>0.00777821359399147</v>
       </c>
-      <c r="C87" s="9">
+      <c r="C87" s="48">
         <f>SUM($B$62:$B87)</f>
         <v>0.229956854194845</v>
       </c>
@@ -6502,11 +6508,11 @@
       <c r="A88" s="3">
         <v>27</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="48">
         <f t="shared" si="6"/>
         <v>0.00770043145805155</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="48">
         <f>SUM($B$62:$B88)</f>
         <v>0.237657285652896</v>
       </c>
@@ -6527,11 +6533,11 @@
       <c r="A89" s="3">
         <v>28</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="48">
         <f t="shared" si="6"/>
         <v>0.00762342714347104</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C89" s="48">
         <f>SUM($B$62:$B89)</f>
         <v>0.245280712796367</v>
       </c>
@@ -6552,11 +6558,11 @@
       <c r="A90" s="3">
         <v>29</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="48">
         <f t="shared" si="6"/>
         <v>0.00754719287203633</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="48">
         <f>SUM($B$62:$B90)</f>
         <v>0.252827905668404</v>
       </c>
@@ -6577,11 +6583,11 @@
       <c r="A91" s="3">
         <v>30</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="48">
         <f t="shared" si="6"/>
         <v>0.00747172094331596</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C91" s="48">
         <f>SUM($B$62:$B91)</f>
         <v>0.26029962661172</v>
       </c>
@@ -6602,11 +6608,11 @@
       <c r="A92" s="3">
         <v>31</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="48">
         <f t="shared" si="6"/>
         <v>0.0073970037338828</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="48">
         <f>SUM($B$62:$B92)</f>
         <v>0.267696630345602</v>
       </c>
@@ -6627,11 +6633,11 @@
       <c r="A93" s="3">
         <v>32</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="48">
         <f t="shared" si="6"/>
         <v>0.00732303369654397</v>
       </c>
-      <c r="C93" s="9">
+      <c r="C93" s="48">
         <f>SUM($B$62:$B93)</f>
         <v>0.275019664042146</v>
       </c>
@@ -6652,11 +6658,11 @@
       <c r="A94" s="3">
         <v>33</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="48">
         <f t="shared" si="6"/>
         <v>0.00724980335957853</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="48">
         <f>SUM($B$62:$B94)</f>
         <v>0.282269467401725</v>
       </c>
@@ -6677,11 +6683,11 @@
       <c r="A95" s="3">
         <v>34</v>
       </c>
-      <c r="B95" s="9">
+      <c r="B95" s="48">
         <f t="shared" si="6"/>
         <v>0.00717730532598275</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C95" s="48">
         <f>SUM($B$62:$B95)</f>
         <v>0.289446772727708</v>
       </c>
@@ -6702,11 +6708,11 @@
       <c r="A96" s="3">
         <v>35</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="48">
         <f t="shared" si="6"/>
         <v>0.00710553227272292</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="48">
         <f>SUM($B$62:$B96)</f>
         <v>0.296552305000431</v>
       </c>
@@ -6727,11 +6733,11 @@
       <c r="A97" s="3">
         <v>36</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="48">
         <f t="shared" si="6"/>
         <v>0.00703447694999569</v>
       </c>
-      <c r="C97" s="9">
+      <c r="C97" s="48">
         <f>SUM($B$62:$B97)</f>
         <v>0.303586781950426</v>
       </c>
@@ -6752,11 +6758,11 @@
       <c r="A98" s="3">
         <v>37</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="48">
         <f t="shared" si="6"/>
         <v>0.00696413218049573</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="48">
         <f>SUM($B$62:$B98)</f>
         <v>0.310550914130922</v>
       </c>
@@ -6777,11 +6783,11 @@
       <c r="A99" s="3">
         <v>38</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="48">
         <f t="shared" si="6"/>
         <v>0.00689449085869078</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99" s="48">
         <f>SUM($B$62:$B99)</f>
         <v>0.317445404989613</v>
       </c>
@@ -6802,11 +6808,11 @@
       <c r="A100" s="3">
         <v>39</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="48">
         <f t="shared" si="6"/>
         <v>0.00682554595010387</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="48">
         <f>SUM($B$62:$B100)</f>
         <v>0.324270950939717</v>
       </c>
@@ -6827,11 +6833,11 @@
       <c r="A101" s="3">
         <v>40</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="48">
         <f t="shared" si="6"/>
         <v>0.00675729049060283</v>
       </c>
-      <c r="C101" s="9">
+      <c r="C101" s="48">
         <f>SUM($B$62:$B101)</f>
         <v>0.331028241430319</v>
       </c>
@@ -6852,11 +6858,11 @@
       <c r="A102" s="3">
         <v>41</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="48">
         <f t="shared" si="6"/>
         <v>0.0066897175856968</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="48">
         <f>SUM($B$62:$B102)</f>
         <v>0.337717959016016</v>
       </c>
@@ -6877,11 +6883,11 @@
       <c r="A103" s="3">
         <v>42</v>
       </c>
-      <c r="B103" s="9">
+      <c r="B103" s="48">
         <f t="shared" si="6"/>
         <v>0.00662282040983983</v>
       </c>
-      <c r="C103" s="9">
+      <c r="C103" s="48">
         <f>SUM($B$62:$B103)</f>
         <v>0.344340779425856</v>
       </c>
@@ -6902,11 +6908,11 @@
       <c r="A104" s="3">
         <v>43</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="48">
         <f t="shared" si="6"/>
         <v>0.00655659220574144</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="48">
         <f>SUM($B$62:$B104)</f>
         <v>0.350897371631598</v>
       </c>
@@ -6927,11 +6933,11 @@
       <c r="A105" s="3">
         <v>44</v>
       </c>
-      <c r="B105" s="9">
+      <c r="B105" s="48">
         <f t="shared" si="6"/>
         <v>0.00649102628368402</v>
       </c>
-      <c r="C105" s="9">
+      <c r="C105" s="48">
         <f>SUM($B$62:$B105)</f>
         <v>0.357388397915282</v>
       </c>
@@ -6952,11 +6958,11 @@
       <c r="A106" s="3">
         <v>45</v>
       </c>
-      <c r="B106" s="9">
+      <c r="B106" s="48">
         <f t="shared" si="6"/>
         <v>0.00642611602084718</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="48">
         <f>SUM($B$62:$B106)</f>
         <v>0.363814513936129</v>
       </c>
@@ -6977,11 +6983,11 @@
       <c r="A107" s="3">
         <v>46</v>
       </c>
-      <c r="B107" s="9">
+      <c r="B107" s="48">
         <f t="shared" si="6"/>
         <v>0.00636185486063871</v>
       </c>
-      <c r="C107" s="9">
+      <c r="C107" s="48">
         <f>SUM($B$62:$B107)</f>
         <v>0.370176368796768</v>
       </c>
@@ -7002,11 +7008,11 @@
       <c r="A108" s="3">
         <v>47</v>
       </c>
-      <c r="B108" s="9">
+      <c r="B108" s="48">
         <f t="shared" si="6"/>
         <v>0.00629823631203232</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108" s="48">
         <f>SUM($B$62:$B108)</f>
         <v>0.3764746051088</v>
       </c>
@@ -7027,11 +7033,11 @@
       <c r="A109" s="3">
         <v>48</v>
       </c>
-      <c r="B109" s="9">
+      <c r="B109" s="48">
         <f t="shared" si="6"/>
         <v>0.006235253948912</v>
       </c>
-      <c r="C109" s="9">
+      <c r="C109" s="48">
         <f>SUM($B$62:$B109)</f>
         <v>0.382709859057712</v>
       </c>
@@ -7052,11 +7058,11 @@
       <c r="A110" s="3">
         <v>49</v>
       </c>
-      <c r="B110" s="9">
+      <c r="B110" s="48">
         <f t="shared" si="6"/>
         <v>0.00617290140942288</v>
       </c>
-      <c r="C110" s="9">
+      <c r="C110" s="48">
         <f>SUM($B$62:$B110)</f>
         <v>0.388882760467135</v>
       </c>
@@ -7077,11 +7083,11 @@
       <c r="A111" s="3">
         <v>50</v>
       </c>
-      <c r="B111" s="9">
+      <c r="B111" s="48">
         <f t="shared" si="6"/>
         <v>0.00611117239532865</v>
       </c>
-      <c r="C111" s="9">
+      <c r="C111" s="48">
         <f>SUM($B$62:$B111)</f>
         <v>0.394993932862463</v>
       </c>
@@ -7102,11 +7108,11 @@
       <c r="A112" s="3">
         <v>51</v>
       </c>
-      <c r="B112" s="9">
+      <c r="B112" s="48">
         <f t="shared" si="6"/>
         <v>0.00605006067137536</v>
       </c>
-      <c r="C112" s="9">
+      <c r="C112" s="48">
         <f>SUM($B$62:$B112)</f>
         <v>0.401043993533839</v>
       </c>
@@ -7127,11 +7133,11 @@
       <c r="A113" s="3">
         <v>52</v>
       </c>
-      <c r="B113" s="9">
+      <c r="B113" s="48">
         <f t="shared" si="6"/>
         <v>0.00598956006466161</v>
       </c>
-      <c r="C113" s="9">
+      <c r="C113" s="48">
         <f>SUM($B$62:$B113)</f>
         <v>0.4070335535985</v>
       </c>
@@ -7152,11 +7158,11 @@
       <c r="A114" s="3">
         <v>53</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="48">
         <f t="shared" si="6"/>
         <v>0.00592966446401499</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C114" s="48">
         <f>SUM($B$62:$B114)</f>
         <v>0.412963218062515</v>
       </c>
@@ -7177,11 +7183,11 @@
       <c r="A115" s="3">
         <v>54</v>
       </c>
-      <c r="B115" s="9">
+      <c r="B115" s="48">
         <f t="shared" si="6"/>
         <v>0.00587036781937484</v>
       </c>
-      <c r="C115" s="9">
+      <c r="C115" s="48">
         <f>SUM($B$62:$B115)</f>
         <v>0.41883358588189</v>
       </c>
@@ -7202,11 +7208,11 @@
       <c r="A116" s="3">
         <v>55</v>
       </c>
-      <c r="B116" s="9">
+      <c r="B116" s="48">
         <f t="shared" si="6"/>
         <v>0.0058116641411811</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C116" s="48">
         <f>SUM($B$62:$B116)</f>
         <v>0.424645250023071</v>
       </c>
@@ -7227,11 +7233,11 @@
       <c r="A117" s="3">
         <v>56</v>
       </c>
-      <c r="B117" s="9">
+      <c r="B117" s="48">
         <f t="shared" si="6"/>
         <v>0.00575354749976929</v>
       </c>
-      <c r="C117" s="9">
+      <c r="C117" s="48">
         <f>SUM($B$62:$B117)</f>
         <v>0.430398797522841</v>
       </c>
@@ -7252,11 +7258,11 @@
       <c r="A118" s="3">
         <v>57</v>
       </c>
-      <c r="B118" s="9">
+      <c r="B118" s="48">
         <f t="shared" si="6"/>
         <v>0.00569601202477159</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C118" s="48">
         <f>SUM($B$62:$B118)</f>
         <v>0.436094809547612</v>
       </c>
@@ -7277,11 +7283,11 @@
       <c r="A119" s="3">
         <v>58</v>
       </c>
-      <c r="B119" s="9">
+      <c r="B119" s="48">
         <f t="shared" si="6"/>
         <v>0.00563905190452388</v>
       </c>
-      <c r="C119" s="9">
+      <c r="C119" s="48">
         <f>SUM($B$62:$B119)</f>
         <v>0.441733861452136</v>
       </c>
@@ -7302,11 +7308,11 @@
       <c r="A120" s="3">
         <v>59</v>
       </c>
-      <c r="B120" s="9">
+      <c r="B120" s="48">
         <f t="shared" si="6"/>
         <v>0.00558266138547864</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C120" s="48">
         <f>SUM($B$62:$B120)</f>
         <v>0.447316522837615</v>
       </c>
@@ -7327,11 +7333,11 @@
       <c r="A121" s="3">
         <v>60</v>
       </c>
-      <c r="B121" s="9">
+      <c r="B121" s="48">
         <f t="shared" si="6"/>
         <v>0.00552683477162385</v>
       </c>
-      <c r="C121" s="9">
+      <c r="C121" s="48">
         <f>SUM($B$62:$B121)</f>
         <v>0.452843357609239</v>
       </c>
@@ -7352,11 +7358,11 @@
       <c r="A122" s="3">
         <v>61</v>
       </c>
-      <c r="B122" s="9">
+      <c r="B122" s="48">
         <f t="shared" si="6"/>
         <v>0.00547156642390761</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C122" s="48">
         <f>SUM($B$62:$B122)</f>
         <v>0.458314924033146</v>
       </c>
@@ -7377,11 +7383,11 @@
       <c r="A123" s="3">
         <v>62</v>
       </c>
-      <c r="B123" s="9">
+      <c r="B123" s="48">
         <f t="shared" si="6"/>
         <v>0.00541685075966854</v>
       </c>
-      <c r="C123" s="9">
+      <c r="C123" s="48">
         <f>SUM($B$62:$B123)</f>
         <v>0.463731774792815</v>
       </c>
@@ -7402,11 +7408,11 @@
       <c r="A124" s="3">
         <v>63</v>
       </c>
-      <c r="B124" s="9">
+      <c r="B124" s="48">
         <f t="shared" si="6"/>
         <v>0.00536268225207185</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C124" s="48">
         <f>SUM($B$62:$B124)</f>
         <v>0.469094457044887</v>
       </c>
@@ -7427,11 +7433,11 @@
       <c r="A125" s="3">
         <v>64</v>
       </c>
-      <c r="B125" s="9">
+      <c r="B125" s="48">
         <f t="shared" si="6"/>
         <v>0.00530905542955113</v>
       </c>
-      <c r="C125" s="9">
+      <c r="C125" s="48">
         <f>SUM($B$62:$B125)</f>
         <v>0.474403512474438</v>
       </c>
@@ -7452,11 +7458,11 @@
       <c r="A126" s="3">
         <v>65</v>
       </c>
-      <c r="B126" s="9">
+      <c r="B126" s="48">
         <f t="shared" ref="B126:B189" si="7">(1-1/$B$59)^($A126-1)*(1/$B$59)</f>
         <v>0.00525596487525562</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C126" s="48">
         <f>SUM($B$62:$B126)</f>
         <v>0.479659477349693</v>
       </c>
@@ -7477,11 +7483,11 @@
       <c r="A127" s="3">
         <v>66</v>
       </c>
-      <c r="B127" s="9">
+      <c r="B127" s="48">
         <f t="shared" si="7"/>
         <v>0.00520340522650306</v>
       </c>
-      <c r="C127" s="9">
+      <c r="C127" s="48">
         <f>SUM($B$62:$B127)</f>
         <v>0.484862882576196</v>
       </c>
@@ -7502,11 +7508,11 @@
       <c r="A128" s="3">
         <v>67</v>
       </c>
-      <c r="B128" s="9">
+      <c r="B128" s="48">
         <f t="shared" si="7"/>
         <v>0.00515137117423803</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C128" s="48">
         <f>SUM($B$62:$B128)</f>
         <v>0.490014253750434</v>
       </c>
@@ -7527,11 +7533,11 @@
       <c r="A129" s="3">
         <v>68</v>
       </c>
-      <c r="B129" s="9">
+      <c r="B129" s="48">
         <f t="shared" si="7"/>
         <v>0.00509985746249565</v>
       </c>
-      <c r="C129" s="9">
+      <c r="C129" s="48">
         <f>SUM($B$62:$B129)</f>
         <v>0.49511411121293</v>
       </c>
@@ -7552,11 +7558,11 @@
       <c r="A130" s="3">
         <v>69</v>
       </c>
-      <c r="B130" s="9">
+      <c r="B130" s="48">
         <f t="shared" si="7"/>
         <v>0.0050488588878707</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C130" s="48">
         <f>SUM($B$62:$B130)</f>
         <v>0.500162970100801</v>
       </c>
@@ -7577,11 +7583,11 @@
       <c r="A131" s="3">
         <v>70</v>
       </c>
-      <c r="B131" s="9">
+      <c r="B131" s="48">
         <f t="shared" si="7"/>
         <v>0.00499837029899199</v>
       </c>
-      <c r="C131" s="9">
+      <c r="C131" s="48">
         <f>SUM($B$62:$B131)</f>
         <v>0.505161340399793</v>
       </c>
@@ -7602,11 +7608,11 @@
       <c r="A132" s="3">
         <v>71</v>
       </c>
-      <c r="B132" s="9">
+      <c r="B132" s="48">
         <f t="shared" si="7"/>
         <v>0.00494838659600207</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C132" s="48">
         <f>SUM($B$62:$B132)</f>
         <v>0.510109726995795</v>
       </c>
@@ -7627,11 +7633,11 @@
       <c r="A133" s="3">
         <v>72</v>
       </c>
-      <c r="B133" s="9">
+      <c r="B133" s="48">
         <f t="shared" si="7"/>
         <v>0.00489890273004205</v>
       </c>
-      <c r="C133" s="9">
+      <c r="C133" s="48">
         <f>SUM($B$62:$B133)</f>
         <v>0.515008629725837</v>
       </c>
@@ -7652,11 +7658,11 @@
       <c r="A134" s="3">
         <v>73</v>
       </c>
-      <c r="B134" s="9">
+      <c r="B134" s="48">
         <f t="shared" si="7"/>
         <v>0.00484991370274163</v>
       </c>
-      <c r="C134" s="9">
+      <c r="C134" s="48">
         <f>SUM($B$62:$B134)</f>
         <v>0.519858543428578</v>
       </c>
@@ -7677,11 +7683,11 @@
       <c r="A135" s="3">
         <v>74</v>
       </c>
-      <c r="B135" s="9">
+      <c r="B135" s="48">
         <f t="shared" si="7"/>
         <v>0.00480141456571421</v>
       </c>
-      <c r="C135" s="9">
+      <c r="C135" s="48">
         <f>SUM($B$62:$B135)</f>
         <v>0.524659957994293</v>
       </c>
@@ -7702,11 +7708,11 @@
       <c r="A136" s="3">
         <v>75</v>
       </c>
-      <c r="B136" s="9">
+      <c r="B136" s="48">
         <f t="shared" si="7"/>
         <v>0.00475340042005707</v>
       </c>
-      <c r="C136" s="9">
+      <c r="C136" s="48">
         <f>SUM($B$62:$B136)</f>
         <v>0.52941335841435</v>
       </c>
@@ -7727,11 +7733,11 @@
       <c r="A137" s="3">
         <v>76</v>
       </c>
-      <c r="B137" s="9">
+      <c r="B137" s="48">
         <f t="shared" si="7"/>
         <v>0.0047058664158565</v>
       </c>
-      <c r="C137" s="9">
+      <c r="C137" s="48">
         <f>SUM($B$62:$B137)</f>
         <v>0.534119224830206</v>
       </c>
@@ -7752,11 +7758,11 @@
       <c r="A138" s="3">
         <v>77</v>
       </c>
-      <c r="B138" s="9">
+      <c r="B138" s="48">
         <f t="shared" si="7"/>
         <v>0.00465880775169793</v>
       </c>
-      <c r="C138" s="9">
+      <c r="C138" s="48">
         <f>SUM($B$62:$B138)</f>
         <v>0.538778032581904</v>
       </c>
@@ -7777,11 +7783,11 @@
       <c r="A139" s="3">
         <v>78</v>
       </c>
-      <c r="B139" s="9">
+      <c r="B139" s="48">
         <f t="shared" si="7"/>
         <v>0.00461221967418095</v>
       </c>
-      <c r="C139" s="9">
+      <c r="C139" s="48">
         <f>SUM($B$62:$B139)</f>
         <v>0.543390252256085</v>
       </c>
@@ -7802,11 +7808,11 @@
       <c r="A140" s="3">
         <v>79</v>
       </c>
-      <c r="B140" s="9">
+      <c r="B140" s="48">
         <f t="shared" si="7"/>
         <v>0.00456609747743915</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C140" s="48">
         <f>SUM($B$62:$B140)</f>
         <v>0.547956349733524</v>
       </c>
@@ -7827,11 +7833,11 @@
       <c r="A141" s="3">
         <v>80</v>
       </c>
-      <c r="B141" s="9">
+      <c r="B141" s="48">
         <f t="shared" si="7"/>
         <v>0.00452043650266475</v>
       </c>
-      <c r="C141" s="9">
+      <c r="C141" s="48">
         <f>SUM($B$62:$B141)</f>
         <v>0.552476786236189</v>
       </c>
@@ -7852,11 +7858,11 @@
       <c r="A142" s="3">
         <v>81</v>
       </c>
-      <c r="B142" s="9">
+      <c r="B142" s="48">
         <f t="shared" si="7"/>
         <v>0.00447523213763811</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C142" s="48">
         <f>SUM($B$62:$B142)</f>
         <v>0.556952018373827</v>
       </c>
@@ -7877,11 +7883,11 @@
       <c r="A143" s="3">
         <v>82</v>
       </c>
-      <c r="B143" s="9">
+      <c r="B143" s="48">
         <f t="shared" si="7"/>
         <v>0.00443047981626173</v>
       </c>
-      <c r="C143" s="9">
+      <c r="C143" s="48">
         <f>SUM($B$62:$B143)</f>
         <v>0.561382498190089</v>
       </c>
@@ -7902,11 +7908,11 @@
       <c r="A144" s="3">
         <v>83</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="48">
         <f t="shared" si="7"/>
         <v>0.00438617501809911</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="48">
         <f>SUM($B$62:$B144)</f>
         <v>0.565768673208188</v>
       </c>
@@ -7927,11 +7933,11 @@
       <c r="A145" s="3">
         <v>84</v>
       </c>
-      <c r="B145" s="9">
+      <c r="B145" s="48">
         <f t="shared" si="7"/>
         <v>0.00434231326791812</v>
       </c>
-      <c r="C145" s="9">
+      <c r="C145" s="48">
         <f>SUM($B$62:$B145)</f>
         <v>0.570110986476106</v>
       </c>
@@ -7952,11 +7958,11 @@
       <c r="A146" s="3">
         <v>85</v>
       </c>
-      <c r="B146" s="9">
+      <c r="B146" s="48">
         <f t="shared" si="7"/>
         <v>0.00429889013523894</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146" s="48">
         <f>SUM($B$62:$B146)</f>
         <v>0.574409876611345</v>
       </c>
@@ -7977,11 +7983,11 @@
       <c r="A147" s="3">
         <v>86</v>
       </c>
-      <c r="B147" s="9">
+      <c r="B147" s="48">
         <f t="shared" si="7"/>
         <v>0.00425590123388655</v>
       </c>
-      <c r="C147" s="9">
+      <c r="C147" s="48">
         <f>SUM($B$62:$B147)</f>
         <v>0.578665777845232</v>
       </c>
@@ -8002,11 +8008,11 @@
       <c r="A148" s="3">
         <v>87</v>
       </c>
-      <c r="B148" s="9">
+      <c r="B148" s="48">
         <f t="shared" si="7"/>
         <v>0.00421334222154768</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C148" s="48">
         <f>SUM($B$62:$B148)</f>
         <v>0.582879120066779</v>
       </c>
@@ -8027,11 +8033,11 @@
       <c r="A149" s="3">
         <v>88</v>
       </c>
-      <c r="B149" s="9">
+      <c r="B149" s="48">
         <f t="shared" si="7"/>
         <v>0.0041712087993322</v>
       </c>
-      <c r="C149" s="9">
+      <c r="C149" s="48">
         <f>SUM($B$62:$B149)</f>
         <v>0.587050328866112</v>
       </c>
@@ -8052,11 +8058,11 @@
       <c r="A150" s="3">
         <v>89</v>
       </c>
-      <c r="B150" s="9">
+      <c r="B150" s="48">
         <f t="shared" si="7"/>
         <v>0.00412949671133888</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C150" s="48">
         <f>SUM($B$62:$B150)</f>
         <v>0.59117982557745</v>
       </c>
@@ -8077,11 +8083,11 @@
       <c r="A151" s="3">
         <v>90</v>
       </c>
-      <c r="B151" s="9">
+      <c r="B151" s="48">
         <f t="shared" si="7"/>
         <v>0.00408820174422549</v>
       </c>
-      <c r="C151" s="9">
+      <c r="C151" s="48">
         <f>SUM($B$62:$B151)</f>
         <v>0.595268027321676</v>
       </c>
@@ -8102,11 +8108,11 @@
       <c r="A152" s="3">
         <v>91</v>
       </c>
-      <c r="B152" s="9">
+      <c r="B152" s="48">
         <f t="shared" si="7"/>
         <v>0.00404731972678324</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C152" s="48">
         <f>SUM($B$62:$B152)</f>
         <v>0.599315347048459</v>
       </c>
@@ -8127,11 +8133,11 @@
       <c r="A153" s="3">
         <v>92</v>
       </c>
-      <c r="B153" s="9">
+      <c r="B153" s="48">
         <f t="shared" si="7"/>
         <v>0.00400684652951541</v>
       </c>
-      <c r="C153" s="9">
+      <c r="C153" s="48">
         <f>SUM($B$62:$B153)</f>
         <v>0.603322193577975</v>
       </c>
@@ -8152,11 +8158,11 @@
       <c r="A154" s="3">
         <v>93</v>
       </c>
-      <c r="B154" s="9">
+      <c r="B154" s="48">
         <f t="shared" si="7"/>
         <v>0.00396677806422025</v>
       </c>
-      <c r="C154" s="9">
+      <c r="C154" s="48">
         <f>SUM($B$62:$B154)</f>
         <v>0.607288971642195</v>
       </c>
@@ -8177,11 +8183,11 @@
       <c r="A155" s="3">
         <v>94</v>
       </c>
-      <c r="B155" s="9">
+      <c r="B155" s="48">
         <f t="shared" si="7"/>
         <v>0.00392711028357805</v>
       </c>
-      <c r="C155" s="9">
+      <c r="C155" s="48">
         <f>SUM($B$62:$B155)</f>
         <v>0.611216081925773</v>
       </c>
@@ -8202,11 +8208,11 @@
       <c r="A156" s="3">
         <v>95</v>
       </c>
-      <c r="B156" s="9">
+      <c r="B156" s="48">
         <f t="shared" si="7"/>
         <v>0.00388783918074227</v>
       </c>
-      <c r="C156" s="9">
+      <c r="C156" s="48">
         <f>SUM($B$62:$B156)</f>
         <v>0.615103921106515</v>
       </c>
@@ -8227,11 +8233,11 @@
       <c r="A157" s="3">
         <v>96</v>
       </c>
-      <c r="B157" s="9">
+      <c r="B157" s="48">
         <f t="shared" si="7"/>
         <v>0.00384896078893485</v>
       </c>
-      <c r="C157" s="9">
+      <c r="C157" s="48">
         <f>SUM($B$62:$B157)</f>
         <v>0.61895288189545</v>
       </c>
@@ -8252,11 +8258,11 @@
       <c r="A158" s="3">
         <v>97</v>
       </c>
-      <c r="B158" s="9">
+      <c r="B158" s="48">
         <f t="shared" si="7"/>
         <v>0.0038104711810455</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C158" s="48">
         <f>SUM($B$62:$B158)</f>
         <v>0.622763353076496</v>
       </c>
@@ -8277,11 +8283,11 @@
       <c r="A159" s="3">
         <v>98</v>
       </c>
-      <c r="B159" s="9">
+      <c r="B159" s="48">
         <f t="shared" si="7"/>
         <v>0.00377236646923504</v>
       </c>
-      <c r="C159" s="9">
+      <c r="C159" s="48">
         <f>SUM($B$62:$B159)</f>
         <v>0.626535719545731</v>
       </c>
@@ -8302,11 +8308,11 @@
       <c r="A160" s="3">
         <v>99</v>
       </c>
-      <c r="B160" s="9">
+      <c r="B160" s="48">
         <f t="shared" si="7"/>
         <v>0.00373464280454269</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160" s="48">
         <f>SUM($B$62:$B160)</f>
         <v>0.630270362350273</v>
       </c>
@@ -8327,11 +8333,11 @@
       <c r="A161" s="3">
         <v>100</v>
       </c>
-      <c r="B161" s="9">
+      <c r="B161" s="48">
         <f t="shared" si="7"/>
         <v>0.00369729637649726</v>
       </c>
-      <c r="C161" s="9">
+      <c r="C161" s="48">
         <f>SUM($B$62:$B161)</f>
         <v>0.633967658726771</v>
       </c>
@@ -8352,11 +8358,11 @@
       <c r="A162" s="3">
         <v>101</v>
       </c>
-      <c r="B162" s="9">
+      <c r="B162" s="48">
         <f t="shared" si="7"/>
         <v>0.00366032341273229</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C162" s="48">
         <f>SUM($B$62:$B162)</f>
         <v>0.637627982139503</v>
       </c>
@@ -8377,11 +8383,11 @@
       <c r="A163" s="3">
         <v>102</v>
       </c>
-      <c r="B163" s="9">
+      <c r="B163" s="48">
         <f t="shared" si="7"/>
         <v>0.00362372017860497</v>
       </c>
-      <c r="C163" s="9">
+      <c r="C163" s="48">
         <f>SUM($B$62:$B163)</f>
         <v>0.641251702318108</v>
       </c>
@@ -8402,11 +8408,11 @@
       <c r="A164" s="3">
         <v>103</v>
       </c>
-      <c r="B164" s="9">
+      <c r="B164" s="48">
         <f t="shared" si="7"/>
         <v>0.00358748297681892</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C164" s="48">
         <f>SUM($B$62:$B164)</f>
         <v>0.644839185294927</v>
       </c>
@@ -8427,11 +8433,11 @@
       <c r="A165" s="3">
         <v>104</v>
       </c>
-      <c r="B165" s="9">
+      <c r="B165" s="48">
         <f t="shared" si="7"/>
         <v>0.00355160814705073</v>
       </c>
-      <c r="C165" s="9">
+      <c r="C165" s="48">
         <f>SUM($B$62:$B165)</f>
         <v>0.648390793441977</v>
       </c>
@@ -8452,11 +8458,11 @@
       <c r="A166" s="3">
         <v>105</v>
       </c>
-      <c r="B166" s="9">
+      <c r="B166" s="48">
         <f t="shared" si="7"/>
         <v>0.00351609206558022</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C166" s="48">
         <f>SUM($B$62:$B166)</f>
         <v>0.651906885507558</v>
       </c>
@@ -8477,11 +8483,11 @@
       <c r="A167" s="3">
         <v>106</v>
       </c>
-      <c r="B167" s="9">
+      <c r="B167" s="48">
         <f t="shared" si="7"/>
         <v>0.00348093114492442</v>
       </c>
-      <c r="C167" s="9">
+      <c r="C167" s="48">
         <f>SUM($B$62:$B167)</f>
         <v>0.655387816652482</v>
       </c>
@@ -8502,11 +8508,11 @@
       <c r="A168" s="3">
         <v>107</v>
       </c>
-      <c r="B168" s="9">
+      <c r="B168" s="48">
         <f t="shared" si="7"/>
         <v>0.00344612183347518</v>
       </c>
-      <c r="C168" s="9">
+      <c r="C168" s="48">
         <f>SUM($B$62:$B168)</f>
         <v>0.658833938485957</v>
       </c>
@@ -8527,11 +8533,11 @@
       <c r="A169" s="3">
         <v>108</v>
       </c>
-      <c r="B169" s="9">
+      <c r="B169" s="48">
         <f t="shared" si="7"/>
         <v>0.00341166061514042</v>
       </c>
-      <c r="C169" s="9">
+      <c r="C169" s="48">
         <f>SUM($B$62:$B169)</f>
         <v>0.662245599101098</v>
       </c>
@@ -8552,11 +8558,11 @@
       <c r="A170" s="3">
         <v>109</v>
       </c>
-      <c r="B170" s="9">
+      <c r="B170" s="48">
         <f t="shared" si="7"/>
         <v>0.00337754400898902</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C170" s="48">
         <f>SUM($B$62:$B170)</f>
         <v>0.665623143110087</v>
       </c>
@@ -8577,11 +8583,11 @@
       <c r="A171" s="3">
         <v>110</v>
       </c>
-      <c r="B171" s="9">
+      <c r="B171" s="48">
         <f t="shared" si="7"/>
         <v>0.00334376856889913</v>
       </c>
-      <c r="C171" s="9">
+      <c r="C171" s="48">
         <f>SUM($B$62:$B171)</f>
         <v>0.668966911678986</v>
       </c>
@@ -8602,11 +8608,11 @@
       <c r="A172" s="3">
         <v>111</v>
       </c>
-      <c r="B172" s="9">
+      <c r="B172" s="48">
         <f t="shared" si="7"/>
         <v>0.00331033088321014</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C172" s="48">
         <f>SUM($B$62:$B172)</f>
         <v>0.672277242562196</v>
       </c>
@@ -8627,11 +8633,11 @@
       <c r="A173" s="3">
         <v>112</v>
       </c>
-      <c r="B173" s="9">
+      <c r="B173" s="48">
         <f t="shared" si="7"/>
         <v>0.00327722757437804</v>
       </c>
-      <c r="C173" s="9">
+      <c r="C173" s="48">
         <f>SUM($B$62:$B173)</f>
         <v>0.675554470136574</v>
       </c>
@@ -8652,11 +8658,11 @@
       <c r="A174" s="3">
         <v>113</v>
       </c>
-      <c r="B174" s="9">
+      <c r="B174" s="48">
         <f t="shared" si="7"/>
         <v>0.00324445529863426</v>
       </c>
-      <c r="C174" s="9">
+      <c r="C174" s="48">
         <f>SUM($B$62:$B174)</f>
         <v>0.678798925435208</v>
       </c>
@@ -8677,11 +8683,11 @@
       <c r="A175" s="3">
         <v>114</v>
       </c>
-      <c r="B175" s="9">
+      <c r="B175" s="48">
         <f t="shared" si="7"/>
         <v>0.00321201074564791</v>
       </c>
-      <c r="C175" s="9">
+      <c r="C175" s="48">
         <f>SUM($B$62:$B175)</f>
         <v>0.682010936180856</v>
       </c>
@@ -8702,11 +8708,11 @@
       <c r="A176" s="3">
         <v>115</v>
       </c>
-      <c r="B176" s="9">
+      <c r="B176" s="48">
         <f t="shared" si="7"/>
         <v>0.00317989063819143</v>
       </c>
-      <c r="C176" s="9">
+      <c r="C176" s="48">
         <f>SUM($B$62:$B176)</f>
         <v>0.685190826819048</v>
       </c>
@@ -8727,11 +8733,11 @@
       <c r="A177" s="3">
         <v>116</v>
       </c>
-      <c r="B177" s="9">
+      <c r="B177" s="48">
         <f t="shared" si="7"/>
         <v>0.00314809173180952</v>
       </c>
-      <c r="C177" s="9">
+      <c r="C177" s="48">
         <f>SUM($B$62:$B177)</f>
         <v>0.688338918550857</v>
       </c>
@@ -8752,11 +8758,11 @@
       <c r="A178" s="3">
         <v>117</v>
       </c>
-      <c r="B178" s="9">
+      <c r="B178" s="48">
         <f t="shared" si="7"/>
         <v>0.00311661081449142</v>
       </c>
-      <c r="C178" s="9">
+      <c r="C178" s="48">
         <f>SUM($B$62:$B178)</f>
         <v>0.691455529365349</v>
       </c>
@@ -8777,11 +8783,11 @@
       <c r="A179" s="3">
         <v>118</v>
       </c>
-      <c r="B179" s="9">
+      <c r="B179" s="48">
         <f t="shared" si="7"/>
         <v>0.00308544470634651</v>
       </c>
-      <c r="C179" s="9">
+      <c r="C179" s="48">
         <f>SUM($B$62:$B179)</f>
         <v>0.694540974071695</v>
       </c>
@@ -8802,11 +8808,11 @@
       <c r="A180" s="3">
         <v>119</v>
       </c>
-      <c r="B180" s="9">
+      <c r="B180" s="48">
         <f t="shared" si="7"/>
         <v>0.00305459025928305</v>
       </c>
-      <c r="C180" s="9">
+      <c r="C180" s="48">
         <f>SUM($B$62:$B180)</f>
         <v>0.697595564330978</v>
       </c>
@@ -8827,11 +8833,11 @@
       <c r="A181" s="3">
         <v>120</v>
       </c>
-      <c r="B181" s="9">
+      <c r="B181" s="48">
         <f t="shared" si="7"/>
         <v>0.00302404435669022</v>
       </c>
-      <c r="C181" s="9">
+      <c r="C181" s="48">
         <f>SUM($B$62:$B181)</f>
         <v>0.700619608687668</v>
       </c>
@@ -8852,11 +8858,11 @@
       <c r="A182" s="3">
         <v>121</v>
       </c>
-      <c r="B182" s="9">
+      <c r="B182" s="48">
         <f t="shared" si="7"/>
         <v>0.00299380391312331</v>
       </c>
-      <c r="C182" s="9">
+      <c r="C182" s="48">
         <f>SUM($B$62:$B182)</f>
         <v>0.703613412600792</v>
       </c>
@@ -8877,11 +8883,11 @@
       <c r="A183" s="3">
         <v>122</v>
       </c>
-      <c r="B183" s="9">
+      <c r="B183" s="48">
         <f t="shared" si="7"/>
         <v>0.00296386587399208</v>
       </c>
-      <c r="C183" s="9">
+      <c r="C183" s="48">
         <f>SUM($B$62:$B183)</f>
         <v>0.706577278474784</v>
       </c>
@@ -8902,11 +8908,11 @@
       <c r="A184" s="3">
         <v>123</v>
       </c>
-      <c r="B184" s="9">
+      <c r="B184" s="48">
         <f t="shared" si="7"/>
         <v>0.00293422721525216</v>
       </c>
-      <c r="C184" s="9">
+      <c r="C184" s="48">
         <f>SUM($B$62:$B184)</f>
         <v>0.709511505690036</v>
       </c>
@@ -8927,11 +8933,11 @@
       <c r="A185" s="3">
         <v>124</v>
       </c>
-      <c r="B185" s="9">
+      <c r="B185" s="48">
         <f t="shared" si="7"/>
         <v>0.00290488494309964</v>
       </c>
-      <c r="C185" s="9">
+      <c r="C185" s="48">
         <f>SUM($B$62:$B185)</f>
         <v>0.712416390633136</v>
       </c>
@@ -8952,11 +8958,11 @@
       <c r="A186" s="3">
         <v>125</v>
       </c>
-      <c r="B186" s="9">
+      <c r="B186" s="48">
         <f t="shared" si="7"/>
         <v>0.00287583609366864</v>
       </c>
-      <c r="C186" s="9">
+      <c r="C186" s="48">
         <f>SUM($B$62:$B186)</f>
         <v>0.715292226726804</v>
       </c>
@@ -8977,11 +8983,11 @@
       <c r="A187" s="3">
         <v>126</v>
       </c>
-      <c r="B187" s="9">
+      <c r="B187" s="48">
         <f t="shared" si="7"/>
         <v>0.00284707773273195</v>
       </c>
-      <c r="C187" s="9">
+      <c r="C187" s="48">
         <f>SUM($B$62:$B187)</f>
         <v>0.718139304459536</v>
       </c>
@@ -9002,11 +9008,11 @@
       <c r="A188" s="3">
         <v>127</v>
       </c>
-      <c r="B188" s="9">
+      <c r="B188" s="48">
         <f t="shared" si="7"/>
         <v>0.00281860695540464</v>
       </c>
-      <c r="C188" s="9">
+      <c r="C188" s="48">
         <f>SUM($B$62:$B188)</f>
         <v>0.720957911414941</v>
       </c>
@@ -9027,11 +9033,11 @@
       <c r="A189" s="3">
         <v>128</v>
       </c>
-      <c r="B189" s="9">
+      <c r="B189" s="48">
         <f t="shared" si="7"/>
         <v>0.00279042088585059</v>
       </c>
-      <c r="C189" s="9">
+      <c r="C189" s="48">
         <f>SUM($B$62:$B189)</f>
         <v>0.723748332300791</v>
       </c>
@@ -9052,11 +9058,11 @@
       <c r="A190" s="3">
         <v>129</v>
       </c>
-      <c r="B190" s="9">
+      <c r="B190" s="48">
         <f t="shared" ref="B190:B253" si="8">(1-1/$B$59)^($A190-1)*(1/$B$59)</f>
         <v>0.00276251667699208</v>
       </c>
-      <c r="C190" s="9">
+      <c r="C190" s="48">
         <f>SUM($B$62:$B190)</f>
         <v>0.726510848977783</v>
       </c>
@@ -9077,11 +9083,11 @@
       <c r="A191" s="3">
         <v>130</v>
       </c>
-      <c r="B191" s="9">
+      <c r="B191" s="48">
         <f t="shared" si="8"/>
         <v>0.00273489151022216</v>
       </c>
-      <c r="C191" s="9">
+      <c r="C191" s="48">
         <f>SUM($B$62:$B191)</f>
         <v>0.729245740488006</v>
       </c>
@@ -9102,11 +9108,11 @@
       <c r="A192" s="3">
         <v>131</v>
       </c>
-      <c r="B192" s="9">
+      <c r="B192" s="48">
         <f t="shared" si="8"/>
         <v>0.00270754259511994</v>
       </c>
-      <c r="C192" s="9">
+      <c r="C192" s="48">
         <f>SUM($B$62:$B192)</f>
         <v>0.731953283083126</v>
       </c>
@@ -9127,11 +9133,11 @@
       <c r="A193" s="3">
         <v>132</v>
       </c>
-      <c r="B193" s="9">
+      <c r="B193" s="48">
         <f t="shared" si="8"/>
         <v>0.00268046716916874</v>
       </c>
-      <c r="C193" s="9">
+      <c r="C193" s="48">
         <f>SUM($B$62:$B193)</f>
         <v>0.734633750252294</v>
       </c>
@@ -9152,11 +9158,11 @@
       <c r="A194" s="3">
         <v>133</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B194" s="48">
         <f t="shared" si="8"/>
         <v>0.00265366249747705</v>
       </c>
-      <c r="C194" s="9">
+      <c r="C194" s="48">
         <f>SUM($B$62:$B194)</f>
         <v>0.737287412749771</v>
       </c>
@@ -9177,11 +9183,11 @@
       <c r="A195" s="3">
         <v>134</v>
       </c>
-      <c r="B195" s="9">
+      <c r="B195" s="48">
         <f t="shared" si="8"/>
         <v>0.00262712587250228</v>
       </c>
-      <c r="C195" s="9">
+      <c r="C195" s="48">
         <f>SUM($B$62:$B195)</f>
         <v>0.739914538622274</v>
       </c>
@@ -9202,11 +9208,11 @@
       <c r="A196" s="3">
         <v>135</v>
       </c>
-      <c r="B196" s="9">
+      <c r="B196" s="48">
         <f t="shared" si="8"/>
         <v>0.00260085461377726</v>
       </c>
-      <c r="C196" s="9">
+      <c r="C196" s="48">
         <f>SUM($B$62:$B196)</f>
         <v>0.742515393236051</v>
       </c>
@@ -9227,11 +9233,11 @@
       <c r="A197" s="3">
         <v>136</v>
       </c>
-      <c r="B197" s="9">
+      <c r="B197" s="48">
         <f t="shared" si="8"/>
         <v>0.00257484606763949</v>
       </c>
-      <c r="C197" s="9">
+      <c r="C197" s="48">
         <f>SUM($B$62:$B197)</f>
         <v>0.74509023930369</v>
       </c>
@@ -9252,11 +9258,11 @@
       <c r="A198" s="3">
         <v>137</v>
       </c>
-      <c r="B198" s="9">
+      <c r="B198" s="48">
         <f t="shared" si="8"/>
         <v>0.00254909760696309</v>
       </c>
-      <c r="C198" s="9">
+      <c r="C198" s="48">
         <f>SUM($B$62:$B198)</f>
         <v>0.747639336910653</v>
       </c>
@@ -9277,11 +9283,11 @@
       <c r="A199" s="3">
         <v>138</v>
       </c>
-      <c r="B199" s="9">
+      <c r="B199" s="48">
         <f t="shared" si="8"/>
         <v>0.00252360663089346</v>
       </c>
-      <c r="C199" s="9">
+      <c r="C199" s="48">
         <f>SUM($B$62:$B199)</f>
         <v>0.750162943541547</v>
       </c>
@@ -9302,11 +9308,11 @@
       <c r="A200" s="3">
         <v>139</v>
       </c>
-      <c r="B200" s="9">
+      <c r="B200" s="48">
         <f t="shared" si="8"/>
         <v>0.00249837056458453</v>
       </c>
-      <c r="C200" s="9">
+      <c r="C200" s="48">
         <f>SUM($B$62:$B200)</f>
         <v>0.752661314106131</v>
       </c>
@@ -9327,11 +9333,11 @@
       <c r="A201" s="3">
         <v>140</v>
       </c>
-      <c r="B201" s="9">
+      <c r="B201" s="48">
         <f t="shared" si="8"/>
         <v>0.00247338685893868</v>
       </c>
-      <c r="C201" s="9">
+      <c r="C201" s="48">
         <f>SUM($B$62:$B201)</f>
         <v>0.75513470096507</v>
       </c>
@@ -9352,11 +9358,11 @@
       <c r="A202" s="3">
         <v>141</v>
       </c>
-      <c r="B202" s="9">
+      <c r="B202" s="48">
         <f t="shared" si="8"/>
         <v>0.00244865299034929</v>
       </c>
-      <c r="C202" s="9">
+      <c r="C202" s="48">
         <f>SUM($B$62:$B202)</f>
         <v>0.757583353955419</v>
       </c>
@@ -9377,11 +9383,11 @@
       <c r="A203" s="3">
         <v>142</v>
       </c>
-      <c r="B203" s="9">
+      <c r="B203" s="48">
         <f t="shared" si="8"/>
         <v>0.0024241664604458</v>
       </c>
-      <c r="C203" s="9">
+      <c r="C203" s="48">
         <f>SUM($B$62:$B203)</f>
         <v>0.760007520415865</v>
       </c>
@@ -9402,11 +9408,11 @@
       <c r="A204" s="3">
         <v>143</v>
       </c>
-      <c r="B204" s="9">
+      <c r="B204" s="48">
         <f t="shared" si="8"/>
         <v>0.00239992479584134</v>
       </c>
-      <c r="C204" s="9">
+      <c r="C204" s="48">
         <f>SUM($B$62:$B204)</f>
         <v>0.762407445211707</v>
       </c>
@@ -9427,11 +9433,11 @@
       <c r="A205" s="3">
         <v>144</v>
       </c>
-      <c r="B205" s="9">
+      <c r="B205" s="48">
         <f t="shared" si="8"/>
         <v>0.00237592554788293</v>
       </c>
-      <c r="C205" s="9">
+      <c r="C205" s="48">
         <f>SUM($B$62:$B205)</f>
         <v>0.764783370759589</v>
       </c>
@@ -9452,11 +9458,11 @@
       <c r="A206" s="3">
         <v>145</v>
       </c>
-      <c r="B206" s="9">
+      <c r="B206" s="48">
         <f t="shared" si="8"/>
         <v>0.0023521662924041</v>
       </c>
-      <c r="C206" s="9">
+      <c r="C206" s="48">
         <f>SUM($B$62:$B206)</f>
         <v>0.767135537051994</v>
       </c>
@@ -9477,11 +9483,11 @@
       <c r="A207" s="3">
         <v>146</v>
       </c>
-      <c r="B207" s="9">
+      <c r="B207" s="48">
         <f t="shared" si="8"/>
         <v>0.00232864462948006</v>
       </c>
-      <c r="C207" s="9">
+      <c r="C207" s="48">
         <f>SUM($B$62:$B207)</f>
         <v>0.769464181681474</v>
       </c>
@@ -9502,11 +9508,11 @@
       <c r="A208" s="3">
         <v>147</v>
       </c>
-      <c r="B208" s="9">
+      <c r="B208" s="48">
         <f t="shared" si="8"/>
         <v>0.00230535818318526</v>
       </c>
-      <c r="C208" s="9">
+      <c r="C208" s="48">
         <f>SUM($B$62:$B208)</f>
         <v>0.771769539864659</v>
       </c>
@@ -9527,11 +9533,11 @@
       <c r="A209" s="3">
         <v>148</v>
       </c>
-      <c r="B209" s="9">
+      <c r="B209" s="48">
         <f t="shared" si="8"/>
         <v>0.00228230460135341</v>
       </c>
-      <c r="C209" s="9">
+      <c r="C209" s="48">
         <f>SUM($B$62:$B209)</f>
         <v>0.774051844466012</v>
       </c>
@@ -9552,11 +9558,11 @@
       <c r="A210" s="3">
         <v>149</v>
       </c>
-      <c r="B210" s="9">
+      <c r="B210" s="48">
         <f t="shared" si="8"/>
         <v>0.00225948155533987</v>
       </c>
-      <c r="C210" s="9">
+      <c r="C210" s="48">
         <f>SUM($B$62:$B210)</f>
         <v>0.776311326021352</v>
       </c>
@@ -9577,11 +9583,11 @@
       <c r="A211" s="3">
         <v>150</v>
       </c>
-      <c r="B211" s="9">
+      <c r="B211" s="48">
         <f t="shared" si="8"/>
         <v>0.00223688673978647</v>
       </c>
-      <c r="C211" s="9">
+      <c r="C211" s="48">
         <f>SUM($B$62:$B211)</f>
         <v>0.778548212761139</v>
       </c>
@@ -9602,11 +9608,11 @@
       <c r="A212" s="3">
         <v>151</v>
       </c>
-      <c r="B212" s="9">
+      <c r="B212" s="48">
         <f t="shared" si="8"/>
         <v>0.00221451787238861</v>
       </c>
-      <c r="C212" s="9">
+      <c r="C212" s="48">
         <f>SUM($B$62:$B212)</f>
         <v>0.780762730633527</v>
       </c>
@@ -9627,11 +9633,11 @@
       <c r="A213" s="3">
         <v>152</v>
       </c>
-      <c r="B213" s="9">
+      <c r="B213" s="48">
         <f t="shared" si="8"/>
         <v>0.00219237269366472</v>
       </c>
-      <c r="C213" s="9">
+      <c r="C213" s="48">
         <f>SUM($B$62:$B213)</f>
         <v>0.782955103327192</v>
       </c>
@@ -9652,11 +9658,11 @@
       <c r="A214" s="3">
         <v>153</v>
       </c>
-      <c r="B214" s="9">
+      <c r="B214" s="48">
         <f t="shared" si="8"/>
         <v>0.00217044896672808</v>
       </c>
-      <c r="C214" s="9">
+      <c r="C214" s="48">
         <f>SUM($B$62:$B214)</f>
         <v>0.78512555229392</v>
       </c>
@@ -9677,11 +9683,11 @@
       <c r="A215" s="3">
         <v>154</v>
       </c>
-      <c r="B215" s="9">
+      <c r="B215" s="48">
         <f t="shared" si="8"/>
         <v>0.0021487444770608</v>
       </c>
-      <c r="C215" s="9">
+      <c r="C215" s="48">
         <f>SUM($B$62:$B215)</f>
         <v>0.787274296770981</v>
       </c>
@@ -9702,11 +9708,11 @@
       <c r="A216" s="3">
         <v>155</v>
       </c>
-      <c r="B216" s="9">
+      <c r="B216" s="48">
         <f t="shared" si="8"/>
         <v>0.00212725703229019</v>
       </c>
-      <c r="C216" s="9">
+      <c r="C216" s="48">
         <f>SUM($B$62:$B216)</f>
         <v>0.789401553803271</v>
       </c>
@@ -9727,11 +9733,11 @@
       <c r="A217" s="3">
         <v>156</v>
       </c>
-      <c r="B217" s="9">
+      <c r="B217" s="48">
         <f t="shared" si="8"/>
         <v>0.00210598446196729</v>
       </c>
-      <c r="C217" s="9">
+      <c r="C217" s="48">
         <f>SUM($B$62:$B217)</f>
         <v>0.791507538265238</v>
       </c>
@@ -9752,11 +9758,11 @@
       <c r="A218" s="3">
         <v>157</v>
       </c>
-      <c r="B218" s="9">
+      <c r="B218" s="48">
         <f t="shared" si="8"/>
         <v>0.00208492461734761</v>
       </c>
-      <c r="C218" s="9">
+      <c r="C218" s="48">
         <f>SUM($B$62:$B218)</f>
         <v>0.793592462882586</v>
       </c>
@@ -9777,11 +9783,11 @@
       <c r="A219" s="3">
         <v>158</v>
       </c>
-      <c r="B219" s="9">
+      <c r="B219" s="48">
         <f t="shared" si="8"/>
         <v>0.00206407537117414</v>
       </c>
-      <c r="C219" s="9">
+      <c r="C219" s="48">
         <f>SUM($B$62:$B219)</f>
         <v>0.79565653825376</v>
       </c>
@@ -9802,11 +9808,11 @@
       <c r="A220" s="3">
         <v>159</v>
       </c>
-      <c r="B220" s="9">
+      <c r="B220" s="48">
         <f t="shared" si="8"/>
         <v>0.00204343461746239</v>
       </c>
-      <c r="C220" s="9">
+      <c r="C220" s="48">
         <f>SUM($B$62:$B220)</f>
         <v>0.797699972871222</v>
       </c>
@@ -9827,11 +9833,11 @@
       <c r="A221" s="3">
         <v>160</v>
       </c>
-      <c r="B221" s="9">
+      <c r="B221" s="48">
         <f t="shared" si="8"/>
         <v>0.00202300027128777</v>
       </c>
-      <c r="C221" s="9">
+      <c r="C221" s="48">
         <f>SUM($B$62:$B221)</f>
         <v>0.79972297314251</v>
       </c>
@@ -9852,11 +9858,11 @@
       <c r="A222" s="3">
         <v>161</v>
       </c>
-      <c r="B222" s="9">
+      <c r="B222" s="48">
         <f t="shared" si="8"/>
         <v>0.00200277026857489</v>
       </c>
-      <c r="C222" s="9">
+      <c r="C222" s="48">
         <f>SUM($B$62:$B222)</f>
         <v>0.801725743411085</v>
       </c>
@@ -9877,11 +9883,11 @@
       <c r="A223" s="3">
         <v>162</v>
       </c>
-      <c r="B223" s="9">
+      <c r="B223" s="48">
         <f t="shared" si="8"/>
         <v>0.00198274256588914</v>
       </c>
-      <c r="C223" s="9">
+      <c r="C223" s="48">
         <f>SUM($B$62:$B223)</f>
         <v>0.803708485976974</v>
       </c>
@@ -9902,11 +9908,11 @@
       <c r="A224" s="3">
         <v>163</v>
       </c>
-      <c r="B224" s="9">
+      <c r="B224" s="48">
         <f t="shared" si="8"/>
         <v>0.00196291514023025</v>
       </c>
-      <c r="C224" s="9">
+      <c r="C224" s="48">
         <f>SUM($B$62:$B224)</f>
         <v>0.805671401117204</v>
       </c>
@@ -9927,11 +9933,11 @@
       <c r="A225" s="3">
         <v>164</v>
       </c>
-      <c r="B225" s="9">
+      <c r="B225" s="48">
         <f t="shared" si="8"/>
         <v>0.00194328598882795</v>
       </c>
-      <c r="C225" s="9">
+      <c r="C225" s="48">
         <f>SUM($B$62:$B225)</f>
         <v>0.807614687106032</v>
       </c>
@@ -9952,11 +9958,11 @@
       <c r="A226" s="3">
         <v>165</v>
       </c>
-      <c r="B226" s="9">
+      <c r="B226" s="48">
         <f t="shared" si="8"/>
         <v>0.00192385312893967</v>
       </c>
-      <c r="C226" s="9">
+      <c r="C226" s="48">
         <f>SUM($B$62:$B226)</f>
         <v>0.809538540234972</v>
       </c>
@@ -9977,11 +9983,11 @@
       <c r="A227" s="3">
         <v>166</v>
       </c>
-      <c r="B227" s="9">
+      <c r="B227" s="48">
         <f t="shared" si="8"/>
         <v>0.00190461459765027</v>
       </c>
-      <c r="C227" s="9">
+      <c r="C227" s="48">
         <f>SUM($B$62:$B227)</f>
         <v>0.811443154832622</v>
       </c>
@@ -10002,11 +10008,11 @@
       <c r="A228" s="3">
         <v>167</v>
       </c>
-      <c r="B228" s="9">
+      <c r="B228" s="48">
         <f t="shared" si="8"/>
         <v>0.00188556845167377</v>
       </c>
-      <c r="C228" s="9">
+      <c r="C228" s="48">
         <f>SUM($B$62:$B228)</f>
         <v>0.813328723284296</v>
       </c>
@@ -10027,11 +10033,11 @@
       <c r="A229" s="3">
         <v>168</v>
       </c>
-      <c r="B229" s="9">
+      <c r="B229" s="48">
         <f t="shared" si="8"/>
         <v>0.00186671276715703</v>
       </c>
-      <c r="C229" s="9">
+      <c r="C229" s="48">
         <f>SUM($B$62:$B229)</f>
         <v>0.815195436051453</v>
       </c>
@@ -10052,11 +10058,11 @@
       <c r="A230" s="3">
         <v>169</v>
       </c>
-      <c r="B230" s="9">
+      <c r="B230" s="48">
         <f t="shared" si="8"/>
         <v>0.00184804563948546</v>
       </c>
-      <c r="C230" s="9">
+      <c r="C230" s="48">
         <f>SUM($B$62:$B230)</f>
         <v>0.817043481690939</v>
       </c>
@@ -10077,11 +10083,11 @@
       <c r="A231" s="3">
         <v>170</v>
       </c>
-      <c r="B231" s="9">
+      <c r="B231" s="48">
         <f t="shared" si="8"/>
         <v>0.00182956518309061</v>
       </c>
-      <c r="C231" s="9">
+      <c r="C231" s="48">
         <f>SUM($B$62:$B231)</f>
         <v>0.818873046874029</v>
       </c>
@@ -10102,11 +10108,11 @@
       <c r="A232" s="3">
         <v>171</v>
       </c>
-      <c r="B232" s="9">
+      <c r="B232" s="48">
         <f t="shared" si="8"/>
         <v>0.0018112695312597</v>
       </c>
-      <c r="C232" s="9">
+      <c r="C232" s="48">
         <f>SUM($B$62:$B232)</f>
         <v>0.820684316405289</v>
       </c>
@@ -10127,11 +10133,11 @@
       <c r="A233" s="3">
         <v>172</v>
       </c>
-      <c r="B233" s="9">
+      <c r="B233" s="48">
         <f t="shared" si="8"/>
         <v>0.00179315683594711</v>
       </c>
-      <c r="C233" s="9">
+      <c r="C233" s="48">
         <f>SUM($B$62:$B233)</f>
         <v>0.822477473241236</v>
       </c>
@@ -10152,11 +10158,11 @@
       <c r="A234" s="3">
         <v>173</v>
       </c>
-      <c r="B234" s="9">
+      <c r="B234" s="48">
         <f t="shared" si="8"/>
         <v>0.00177522526758763</v>
       </c>
-      <c r="C234" s="9">
+      <c r="C234" s="48">
         <f>SUM($B$62:$B234)</f>
         <v>0.824252698508824</v>
       </c>
@@ -10177,11 +10183,11 @@
       <c r="A235" s="3">
         <v>174</v>
       </c>
-      <c r="B235" s="9">
+      <c r="B235" s="48">
         <f t="shared" si="8"/>
         <v>0.00175747301491176</v>
       </c>
-      <c r="C235" s="9">
+      <c r="C235" s="48">
         <f>SUM($B$62:$B235)</f>
         <v>0.826010171523735</v>
       </c>
@@ -10202,11 +10208,11 @@
       <c r="A236" s="3">
         <v>175</v>
       </c>
-      <c r="B236" s="9">
+      <c r="B236" s="48">
         <f t="shared" si="8"/>
         <v>0.00173989828476264</v>
       </c>
-      <c r="C236" s="9">
+      <c r="C236" s="48">
         <f>SUM($B$62:$B236)</f>
         <v>0.827750069808498</v>
       </c>
@@ -10227,11 +10233,11 @@
       <c r="A237" s="3">
         <v>176</v>
       </c>
-      <c r="B237" s="9">
+      <c r="B237" s="48">
         <f t="shared" si="8"/>
         <v>0.00172249930191501</v>
       </c>
-      <c r="C237" s="9">
+      <c r="C237" s="48">
         <f>SUM($B$62:$B237)</f>
         <v>0.829472569110413</v>
       </c>
@@ -10252,11 +10258,11 @@
       <c r="A238" s="3">
         <v>177</v>
       </c>
-      <c r="B238" s="9">
+      <c r="B238" s="48">
         <f t="shared" si="8"/>
         <v>0.00170527430889586</v>
       </c>
-      <c r="C238" s="9">
+      <c r="C238" s="48">
         <f>SUM($B$62:$B238)</f>
         <v>0.831177843419309</v>
       </c>
@@ -10277,11 +10283,11 @@
       <c r="A239" s="3">
         <v>178</v>
       </c>
-      <c r="B239" s="9">
+      <c r="B239" s="48">
         <f t="shared" si="8"/>
         <v>0.0016882215658069</v>
       </c>
-      <c r="C239" s="9">
+      <c r="C239" s="48">
         <f>SUM($B$62:$B239)</f>
         <v>0.832866064985116</v>
       </c>
@@ -10302,11 +10308,11 @@
       <c r="A240" s="3">
         <v>179</v>
       </c>
-      <c r="B240" s="9">
+      <c r="B240" s="48">
         <f t="shared" si="8"/>
         <v>0.00167133935014884</v>
       </c>
-      <c r="C240" s="9">
+      <c r="C240" s="48">
         <f>SUM($B$62:$B240)</f>
         <v>0.834537404335265</v>
       </c>
@@ -10327,11 +10333,11 @@
       <c r="A241" s="3">
         <v>180</v>
       </c>
-      <c r="B241" s="9">
+      <c r="B241" s="48">
         <f t="shared" si="8"/>
         <v>0.00165462595664735</v>
       </c>
-      <c r="C241" s="9">
+      <c r="C241" s="48">
         <f>SUM($B$62:$B241)</f>
         <v>0.836192030291912</v>
       </c>
@@ -10352,11 +10358,11 @@
       <c r="A242" s="3">
         <v>181</v>
       </c>
-      <c r="B242" s="9">
+      <c r="B242" s="48">
         <f t="shared" si="8"/>
         <v>0.00163807969708087</v>
       </c>
-      <c r="C242" s="9">
+      <c r="C242" s="48">
         <f>SUM($B$62:$B242)</f>
         <v>0.837830109988993</v>
       </c>
@@ -10377,11 +10383,11 @@
       <c r="A243" s="3">
         <v>182</v>
       </c>
-      <c r="B243" s="9">
+      <c r="B243" s="48">
         <f t="shared" si="8"/>
         <v>0.00162169890011007</v>
       </c>
-      <c r="C243" s="9">
+      <c r="C243" s="48">
         <f>SUM($B$62:$B243)</f>
         <v>0.839451808889103</v>
       </c>
@@ -10402,11 +10408,11 @@
       <c r="A244" s="3">
         <v>183</v>
       </c>
-      <c r="B244" s="9">
+      <c r="B244" s="48">
         <f t="shared" si="8"/>
         <v>0.00160548191110896</v>
       </c>
-      <c r="C244" s="9">
+      <c r="C244" s="48">
         <f>SUM($B$62:$B244)</f>
         <v>0.841057290800212</v>
       </c>
@@ -10427,11 +10433,11 @@
       <c r="A245" s="3">
         <v>184</v>
       </c>
-      <c r="B245" s="9">
+      <c r="B245" s="48">
         <f t="shared" si="8"/>
         <v>0.00158942709199788</v>
       </c>
-      <c r="C245" s="9">
+      <c r="C245" s="48">
         <f>SUM($B$62:$B245)</f>
         <v>0.84264671789221</v>
       </c>
@@ -10452,11 +10458,11 @@
       <c r="A246" s="3">
         <v>185</v>
       </c>
-      <c r="B246" s="9">
+      <c r="B246" s="48">
         <f t="shared" si="8"/>
         <v>0.0015735328210779</v>
       </c>
-      <c r="C246" s="9">
+      <c r="C246" s="48">
         <f>SUM($B$62:$B246)</f>
         <v>0.844220250713288</v>
       </c>
@@ -10477,11 +10483,11 @@
       <c r="A247" s="3">
         <v>186</v>
       </c>
-      <c r="B247" s="9">
+      <c r="B247" s="48">
         <f t="shared" si="8"/>
         <v>0.00155779749286712</v>
       </c>
-      <c r="C247" s="9">
+      <c r="C247" s="48">
         <f>SUM($B$62:$B247)</f>
         <v>0.845778048206155</v>
       </c>
@@ -10502,11 +10508,11 @@
       <c r="A248" s="3">
         <v>187</v>
       </c>
-      <c r="B248" s="9">
+      <c r="B248" s="48">
         <f t="shared" si="8"/>
         <v>0.00154221951793845</v>
       </c>
-      <c r="C248" s="9">
+      <c r="C248" s="48">
         <f>SUM($B$62:$B248)</f>
         <v>0.847320267724093</v>
       </c>
@@ -10527,11 +10533,11 @@
       <c r="A249" s="3">
         <v>188</v>
       </c>
-      <c r="B249" s="9">
+      <c r="B249" s="48">
         <f t="shared" si="8"/>
         <v>0.00152679732275906</v>
       </c>
-      <c r="C249" s="9">
+      <c r="C249" s="48">
         <f>SUM($B$62:$B249)</f>
         <v>0.848847065046852</v>
       </c>
@@ -10552,11 +10558,11 @@
       <c r="A250" s="3">
         <v>189</v>
       </c>
-      <c r="B250" s="9">
+      <c r="B250" s="48">
         <f t="shared" si="8"/>
         <v>0.00151152934953147</v>
       </c>
-      <c r="C250" s="9">
+      <c r="C250" s="48">
         <f>SUM($B$62:$B250)</f>
         <v>0.850358594396384</v>
       </c>
@@ -10577,11 +10583,11 @@
       <c r="A251" s="3">
         <v>190</v>
       </c>
-      <c r="B251" s="9">
+      <c r="B251" s="48">
         <f t="shared" si="8"/>
         <v>0.00149641405603616</v>
       </c>
-      <c r="C251" s="9">
+      <c r="C251" s="48">
         <f>SUM($B$62:$B251)</f>
         <v>0.85185500845242</v>
       </c>
@@ -10602,11 +10608,11 @@
       <c r="A252" s="3">
         <v>191</v>
       </c>
-      <c r="B252" s="9">
+      <c r="B252" s="48">
         <f t="shared" si="8"/>
         <v>0.00148144991547579</v>
       </c>
-      <c r="C252" s="9">
+      <c r="C252" s="48">
         <f>SUM($B$62:$B252)</f>
         <v>0.853336458367896</v>
       </c>
@@ -10627,11 +10633,11 @@
       <c r="A253" s="3">
         <v>192</v>
       </c>
-      <c r="B253" s="9">
+      <c r="B253" s="48">
         <f t="shared" si="8"/>
         <v>0.00146663541632104</v>
       </c>
-      <c r="C253" s="9">
+      <c r="C253" s="48">
         <f>SUM($B$62:$B253)</f>
         <v>0.854803093784217</v>
       </c>
@@ -10652,11 +10658,11 @@
       <c r="A254" s="3">
         <v>193</v>
       </c>
-      <c r="B254" s="9">
+      <c r="B254" s="48">
         <f t="shared" ref="B254:B261" si="9">(1-1/$B$59)^($A254-1)*(1/$B$59)</f>
         <v>0.00145196906215783</v>
       </c>
-      <c r="C254" s="9">
+      <c r="C254" s="48">
         <f>SUM($B$62:$B254)</f>
         <v>0.856255062846375</v>
       </c>
@@ -10677,11 +10683,11 @@
       <c r="A255" s="3">
         <v>194</v>
       </c>
-      <c r="B255" s="9">
+      <c r="B255" s="48">
         <f t="shared" si="9"/>
         <v>0.00143744937153625</v>
       </c>
-      <c r="C255" s="9">
+      <c r="C255" s="48">
         <f>SUM($B$62:$B255)</f>
         <v>0.857692512217911</v>
       </c>
@@ -10702,11 +10708,11 @@
       <c r="A256" s="3">
         <v>195</v>
       </c>
-      <c r="B256" s="9">
+      <c r="B256" s="48">
         <f t="shared" si="9"/>
         <v>0.00142307487782089</v>
       </c>
-      <c r="C256" s="9">
+      <c r="C256" s="48">
         <f>SUM($B$62:$B256)</f>
         <v>0.859115587095732</v>
       </c>
@@ -10727,11 +10733,11 @@
       <c r="A257" s="3">
         <v>196</v>
       </c>
-      <c r="B257" s="9">
+      <c r="B257" s="48">
         <f t="shared" si="9"/>
         <v>0.00140884412904268</v>
       </c>
-      <c r="C257" s="9">
+      <c r="C257" s="48">
         <f>SUM($B$62:$B257)</f>
         <v>0.860524431224774</v>
       </c>
@@ -10752,11 +10758,11 @@
       <c r="A258" s="3">
         <v>197</v>
       </c>
-      <c r="B258" s="9">
+      <c r="B258" s="48">
         <f t="shared" si="9"/>
         <v>0.00139475568775225</v>
       </c>
-      <c r="C258" s="9">
+      <c r="C258" s="48">
         <f>SUM($B$62:$B258)</f>
         <v>0.861919186912527</v>
       </c>
@@ -10777,11 +10783,11 @@
       <c r="A259" s="3">
         <v>198</v>
       </c>
-      <c r="B259" s="9">
+      <c r="B259" s="48">
         <f t="shared" si="9"/>
         <v>0.00138080813087473</v>
       </c>
-      <c r="C259" s="9">
+      <c r="C259" s="48">
         <f>SUM($B$62:$B259)</f>
         <v>0.863299995043401</v>
       </c>
@@ -10802,11 +10808,11 @@
       <c r="A260" s="3">
         <v>199</v>
       </c>
-      <c r="B260" s="9">
+      <c r="B260" s="48">
         <f t="shared" si="9"/>
         <v>0.00136700004956598</v>
       </c>
-      <c r="C260" s="9">
+      <c r="C260" s="48">
         <f>SUM($B$62:$B260)</f>
         <v>0.864666995092967</v>
       </c>
@@ -10827,11 +10833,11 @@
       <c r="A261" s="3">
         <v>200</v>
       </c>
-      <c r="B261" s="9">
+      <c r="B261" s="48">
         <f t="shared" si="9"/>
         <v>0.00135333004907032</v>
       </c>
-      <c r="C261" s="9">
+      <c r="C261" s="48">
         <f>SUM($B$62:$B261)</f>
         <v>0.866020325142038</v>
       </c>
